--- a/21-10-2026/PAT_Berth_Window.xlsx
+++ b/21-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -736,13 +745,13 @@
       <c r="C4" s="17" t="n">
         <v>481</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46316.08333333334</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46316.375</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46316.91666666666</v>
       </c>
       <c r="G4" s="26">
@@ -778,13 +787,13 @@
       <c r="C5" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="D5" s="41" t="n">
+      <c r="D5" s="44" t="n">
         <v>46316.91666666666</v>
       </c>
-      <c r="E5" s="41" t="n">
+      <c r="E5" s="44" t="n">
         <v>46317.54166666666</v>
       </c>
-      <c r="F5" s="41" t="n">
+      <c r="F5" s="44" t="n">
         <v>46318.66666666666</v>
       </c>
       <c r="G5" s="24">
@@ -816,13 +825,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="44" t="n">
         <v>46317.58333333334</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="44" t="n">
         <v>46318.58333333334</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="44" t="n">
         <v>46320.08333333334</v>
       </c>
       <c r="G6" s="24">
@@ -854,13 +863,13 @@
       <c r="C7" s="23" t="n">
         <v>485</v>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="44" t="n">
         <v>46316.54166666666</v>
       </c>
-      <c r="E7" s="41" t="n">
+      <c r="E7" s="44" t="n">
         <v>46316.54166666666</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="44" t="n">
         <v>46317.20833333334</v>
       </c>
       <c r="G7" s="24">
@@ -892,13 +901,13 @@
       <c r="C8" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="44" t="n">
         <v>46316.58333333334</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="44" t="n">
         <v>46317.58333333334</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="44" t="n">
         <v>46318.54166666666</v>
       </c>
       <c r="G8" s="24">
@@ -930,13 +939,13 @@
       <c r="C9" s="23" t="n">
         <v>548</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="44" t="n">
         <v>46317.70833333334</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E9" s="44" t="n">
         <v>46318.54166666666</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="44" t="n">
         <v>46320</v>
       </c>
       <c r="G9" s="24">
@@ -968,13 +977,13 @@
       <c r="C10" s="23" t="n">
         <v>558</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="44" t="n">
         <v>46316.45833333334</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="44" t="n">
         <v>46316.5</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="44" t="n">
         <v>46318.5</v>
       </c>
       <c r="G10" s="24">
@@ -1006,13 +1015,13 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="44" t="n">
         <v>46318.04166666666</v>
       </c>
-      <c r="E11" s="41" t="n">
+      <c r="E11" s="44" t="n">
         <v>46318.5</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="44" t="n">
         <v>46319.625</v>
       </c>
       <c r="G11" s="24">
@@ -1044,13 +1053,13 @@
       <c r="C12" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46315.625</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46315.75</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46316.83333333334</v>
       </c>
       <c r="G12" s="26">
@@ -1086,13 +1095,13 @@
       <c r="C13" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D13" s="44" t="n">
         <v>46316.91666666666</v>
       </c>
-      <c r="E13" s="41" t="n">
+      <c r="E13" s="44" t="n">
         <v>46317.54166666666</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="44" t="n">
         <v>46319.04166666666</v>
       </c>
       <c r="G13" s="24">
@@ -1124,13 +1133,13 @@
       <c r="C14" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D14" s="44" t="n">
         <v>46315.75</v>
       </c>
-      <c r="E14" s="41" t="n">
+      <c r="E14" s="44" t="n">
         <v>46317.41666666666</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="44" t="n">
         <v>46318.41666666666</v>
       </c>
       <c r="G14" s="24">
@@ -1162,13 +1171,13 @@
       <c r="C15" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="44" t="n">
         <v>46318.41666666666</v>
       </c>
-      <c r="E15" s="41" t="n">
+      <c r="E15" s="44" t="n">
         <v>46318.41666666666</v>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F15" s="44" t="n">
         <v>46319.58333333334</v>
       </c>
       <c r="G15" s="24">
@@ -1200,13 +1209,13 @@
       <c r="C16" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="44" t="n">
         <v>46317.29166666666</v>
       </c>
-      <c r="E16" s="41" t="n">
+      <c r="E16" s="44" t="n">
         <v>46317.66666666666</v>
       </c>
-      <c r="F16" s="41" t="n">
+      <c r="F16" s="44" t="n">
         <v>46318.41666666666</v>
       </c>
       <c r="G16" s="24">
@@ -1225,7 +1234,7 @@
       <c r="J16" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1258,13 +1267,13 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="36" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>No notices on this sheet</t>
         </is>
